--- a/logs/multi_sts_cases.xlsx
+++ b/logs/multi_sts_cases.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K487"/>
+  <dimension ref="A1:K481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
+          <t>Zhou Da You 7</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
           <t>Yicheng27</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Zhou Da You 7</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
+          <t>Xin Sheng 17</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
           <t>Kang--Fa--125</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>Xin Sheng 17</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
+          <t>Hai Xiang 17</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
           <t>Kang--Fa--125</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>Hai Xiang 17</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
+          <t>Hongheng169</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
           <t>Zhou Shun 10</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>Hongheng169</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
@@ -8878,12 +8878,12 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
+          <t>Yuan Xiang You 16</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
           <t>Tian Sheng You 19</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E330" t="inlineStr"/>
@@ -9121,19 +9121,19 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="B340" t="n">
         <v>2</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Hui Chen 118</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Shun Ping 17</t>
         </is>
       </c>
       <c r="E340" t="inlineStr"/>
@@ -9146,19 +9146,19 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>1139</v>
+        <v>1145</v>
       </c>
       <c r="B341" t="n">
         <v>2</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
+          <t>Shun Ping 17</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
           <t>Yuan Xiang You 16</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>Shun Ping 17</t>
         </is>
       </c>
       <c r="E341" t="inlineStr"/>
@@ -9171,7 +9171,7 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>1145</v>
+        <v>1151</v>
       </c>
       <c r="B342" t="n">
         <v>2</v>
@@ -9196,19 +9196,19 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="B343" t="n">
         <v>2</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
+          <t>Yuan Xiang You 16</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
           <t>Shun Ping 17</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E343" t="inlineStr"/>
@@ -9221,7 +9221,7 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>1151</v>
+        <v>1161</v>
       </c>
       <c r="B344" t="n">
         <v>2</v>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Shun Ping 17</t>
+          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="E344" t="inlineStr"/>
@@ -9246,19 +9246,19 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>1152</v>
+        <v>1163</v>
       </c>
       <c r="B345" t="n">
         <v>2</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
+          <t>Tian Sheng You 19</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
           <t>Yuan Xiang You 16</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>Shun Ping 17</t>
         </is>
       </c>
       <c r="E345" t="inlineStr"/>
@@ -9271,19 +9271,19 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="B346" t="n">
         <v>2</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
+          <t>Shun Ping 17</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
           <t>Yuan Xiang You 16</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="E346" t="inlineStr"/>
@@ -9296,19 +9296,19 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>1163</v>
+        <v>1169</v>
       </c>
       <c r="B347" t="n">
         <v>2</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
+          <t>Yuan Xiang You 16</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
           <t>Tian Sheng You 19</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E347" t="inlineStr"/>
@@ -9321,14 +9321,14 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>1164</v>
+        <v>1170</v>
       </c>
       <c r="B348" t="n">
         <v>2</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Shun Ping 17</t>
+          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -9346,19 +9346,19 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="B349" t="n">
         <v>2</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Hongheng169</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
+          <t>Shun Kai 7</t>
         </is>
       </c>
       <c r="E349" t="inlineStr"/>
@@ -9371,19 +9371,19 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="B350" t="n">
         <v>2</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
+          <t>Yuan Xiang You 16</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
           <t>Tian Sheng You 19</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E350" t="inlineStr"/>
@@ -9396,19 +9396,19 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B351" t="n">
         <v>2</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Shun Kai 7</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E351" t="inlineStr"/>
@@ -9421,19 +9421,19 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="B352" t="n">
         <v>2</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Yicheng27</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="E352" t="inlineStr"/>
@@ -9446,7 +9446,7 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>1174</v>
+        <v>1177</v>
       </c>
       <c r="B353" t="n">
         <v>2</v>
@@ -9471,19 +9471,19 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="B354" t="n">
         <v>2</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Yicheng27</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Hongheng169</t>
         </is>
       </c>
       <c r="E354" t="inlineStr"/>
@@ -9496,7 +9496,7 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="B355" t="n">
         <v>2</v>
@@ -9521,19 +9521,19 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>1178</v>
+        <v>1182</v>
       </c>
       <c r="B356" t="n">
         <v>2</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Zhoushun5</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Zhoushun5</t>
         </is>
       </c>
       <c r="E356" t="inlineStr"/>
@@ -9546,19 +9546,19 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>1179</v>
+        <v>1183</v>
       </c>
       <c r="B357" t="n">
         <v>2</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Xin Ke 16</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
+          <t>Xin Ke 16</t>
         </is>
       </c>
       <c r="E357" t="inlineStr"/>
@@ -9571,19 +9571,19 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="B358" t="n">
         <v>2</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Zhoushun5</t>
+          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Zhoushun5</t>
+          <t>Zhe Hai You 5</t>
         </is>
       </c>
       <c r="E358" t="inlineStr"/>
@@ -9596,19 +9596,19 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>1183</v>
+        <v>1187</v>
       </c>
       <c r="B359" t="n">
         <v>2</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Xin Ke 16</t>
+          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Xin Ke 16</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E359" t="inlineStr"/>
@@ -9621,7 +9621,7 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>1184</v>
+        <v>1190</v>
       </c>
       <c r="B360" t="n">
         <v>2</v>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Zhe Hai You 5</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E360" t="inlineStr"/>
@@ -9646,14 +9646,14 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>1187</v>
+        <v>1196</v>
       </c>
       <c r="B361" t="n">
         <v>2</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -9671,22 +9671,26 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>1190</v>
+        <v>1201</v>
       </c>
       <c r="B362" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
+          <t>Hai Xiang 17</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
+          <t>Hai Xiang 17</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
           <t>Yuan Xiang You 16</t>
         </is>
       </c>
-      <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr"/>
       <c r="G362" t="inlineStr"/>
       <c r="H362" t="inlineStr"/>
@@ -9696,19 +9700,19 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>1196</v>
+        <v>1206</v>
       </c>
       <c r="B363" t="n">
         <v>2</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
+          <t>Hongheng169</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
           <t>Heng Xing 9</t>
-        </is>
-      </c>
-      <c r="D363" t="inlineStr">
-        <is>
-          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E363" t="inlineStr"/>
@@ -9721,26 +9725,22 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>1201</v>
+        <v>1207</v>
       </c>
       <c r="B364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Hai Xiang 17</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Hai Xiang 17</t>
-        </is>
-      </c>
-      <c r="E364" t="inlineStr">
-        <is>
-          <t>Yuan Xiang You 16</t>
-        </is>
-      </c>
+          <t>Tian Sheng You 19</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr"/>
       <c r="G364" t="inlineStr"/>
       <c r="H364" t="inlineStr"/>
@@ -9750,19 +9750,19 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>1206</v>
+        <v>1213</v>
       </c>
       <c r="B365" t="n">
         <v>2</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
@@ -9775,19 +9775,19 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>1207</v>
+        <v>1216</v>
       </c>
       <c r="B366" t="n">
         <v>2</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
+          <t>Tian Sheng You 19</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
           <t>Yuan Xiang You 16</t>
-        </is>
-      </c>
-      <c r="D366" t="inlineStr">
-        <is>
-          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
@@ -9800,19 +9800,19 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="B367" t="n">
         <v>2</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
+          <t>Yuan Xiang You 16</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
           <t>Tian Sheng You 19</t>
-        </is>
-      </c>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E367" t="inlineStr"/>
@@ -9825,19 +9825,19 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>1216</v>
+        <v>1220</v>
       </c>
       <c r="B368" t="n">
         <v>2</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
+          <t>Hua Guang 68</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Run Ji 17</t>
         </is>
       </c>
       <c r="E368" t="inlineStr"/>
@@ -9850,19 +9850,19 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="B369" t="n">
         <v>2</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Run Ji 17</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
+          <t>Run Ji 15</t>
         </is>
       </c>
       <c r="E369" t="inlineStr"/>
@@ -9875,19 +9875,19 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>1220</v>
+        <v>1225</v>
       </c>
       <c r="B370" t="n">
         <v>2</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Hua Guang 68</t>
+          <t>Hai Xiang 17</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Run Ji 17</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E370" t="inlineStr"/>
@@ -9900,19 +9900,19 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>1222</v>
+        <v>1226</v>
       </c>
       <c r="B371" t="n">
         <v>2</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Run Ji 17</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Run Ji 15</t>
+          <t>Rui Yun 21</t>
         </is>
       </c>
       <c r="E371" t="inlineStr"/>
@@ -9925,19 +9925,19 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="B372" t="n">
         <v>2</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Hai Xiang 17</t>
+          <t>Hongheng189</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Hong Da Hai 88</t>
         </is>
       </c>
       <c r="E372" t="inlineStr"/>
@@ -9950,19 +9950,19 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="B373" t="n">
         <v>2</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
+          <t>Tian Sheng You 19</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
           <t>Yuan Xiang You 16</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>Rui Yun 21</t>
         </is>
       </c>
       <c r="E373" t="inlineStr"/>
@@ -9975,19 +9975,19 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="B374" t="n">
         <v>2</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Hongheng189</t>
+          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Hong Da Hai 88</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E374" t="inlineStr"/>
@@ -10000,14 +10000,14 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>1229</v>
+        <v>1235</v>
       </c>
       <c r="B375" t="n">
         <v>2</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
+          <t>Yicheng27</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -10025,19 +10025,19 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>1230</v>
+        <v>1237</v>
       </c>
       <c r="B376" t="n">
         <v>2</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Xin Sheng 17</t>
         </is>
       </c>
       <c r="E376" t="inlineStr"/>
@@ -10050,19 +10050,19 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>1235</v>
+        <v>1241</v>
       </c>
       <c r="B377" t="n">
         <v>2</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Yicheng27</t>
+          <t>Hongheng169</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
@@ -10075,19 +10075,19 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>1237</v>
+        <v>1243</v>
       </c>
       <c r="B378" t="n">
         <v>2</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Xin Sheng 17</t>
+          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="E378" t="inlineStr"/>
@@ -10100,19 +10100,19 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>1241</v>
+        <v>1251</v>
       </c>
       <c r="B379" t="n">
         <v>2</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="E379" t="inlineStr"/>
@@ -10125,19 +10125,19 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>1243</v>
+        <v>1252</v>
       </c>
       <c r="B380" t="n">
         <v>2</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Hongheng169</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
+          <t>Shun Kai 7</t>
         </is>
       </c>
       <c r="E380" t="inlineStr"/>
@@ -10150,7 +10150,7 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>1251</v>
+        <v>1254</v>
       </c>
       <c r="B381" t="n">
         <v>2</v>
@@ -10162,7 +10162,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
+          <t>Qi Chen 6</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
@@ -10175,19 +10175,19 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="B382" t="n">
         <v>2</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Shun Kai 7</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
@@ -10200,19 +10200,19 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="B383" t="n">
         <v>2</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
+          <t>Heng Xing 9</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
           <t>Yuan Xiang You 16</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>Qi Chen 6</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
@@ -10225,7 +10225,7 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="B384" t="n">
         <v>2</v>
@@ -10250,7 +10250,7 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="B385" t="n">
         <v>2</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Xin Sheng 17</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
@@ -10275,19 +10275,19 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>1258</v>
+        <v>1263</v>
       </c>
       <c r="B386" t="n">
         <v>2</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Xin Ke 16</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Hui Chen 118</t>
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
@@ -10300,19 +10300,19 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="B387" t="n">
         <v>2</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
+          <t>Yuan Xiang You 16</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
           <t>Heng Xing 9</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>Xin Sheng 17</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
@@ -10325,19 +10325,19 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>1263</v>
+        <v>1268</v>
       </c>
       <c r="B388" t="n">
         <v>2</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Xin Ke 16</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Hui Chen 118</t>
+          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
@@ -10350,19 +10350,19 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>1265</v>
+        <v>1271</v>
       </c>
       <c r="B389" t="n">
         <v>2</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Xin Ke 16</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Hui Chen 118</t>
         </is>
       </c>
       <c r="E389" t="inlineStr"/>
@@ -10375,19 +10375,19 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>1268</v>
+        <v>1282</v>
       </c>
       <c r="B390" t="n">
         <v>2</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
+          <t>Hongheng169</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
           <t>Yuan Xiang You 16</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="E390" t="inlineStr"/>
@@ -10400,19 +10400,19 @@
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>1271</v>
+        <v>1283</v>
       </c>
       <c r="B391" t="n">
         <v>2</v>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Xin Ke 16</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Hui Chen 118</t>
+          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="E391" t="inlineStr"/>
@@ -10425,7 +10425,7 @@
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>1282</v>
+        <v>1286</v>
       </c>
       <c r="B392" t="n">
         <v>2</v>
@@ -10450,19 +10450,19 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>1283</v>
+        <v>1288</v>
       </c>
       <c r="B393" t="n">
         <v>2</v>
       </c>
       <c r="C393" t="inlineStr">
         <is>
+          <t>Tian Sheng You 19</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
           <t>Yuan Xiang You 16</t>
-        </is>
-      </c>
-      <c r="D393" t="inlineStr">
-        <is>
-          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="E393" t="inlineStr"/>
@@ -10475,14 +10475,14 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="B394" t="n">
         <v>2</v>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Qi Chen 6</t>
+          <t>Xin Run 20</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -10500,19 +10500,19 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>1286</v>
+        <v>1298</v>
       </c>
       <c r="B395" t="n">
         <v>2</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Hai Hang You 7</t>
         </is>
       </c>
       <c r="E395" t="inlineStr"/>
@@ -10525,19 +10525,19 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>1288</v>
+        <v>1300</v>
       </c>
       <c r="B396" t="n">
         <v>2</v>
       </c>
       <c r="C396" t="inlineStr">
         <is>
+          <t>Yuan Xiang You 16</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
           <t>Tian Sheng You 19</t>
-        </is>
-      </c>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E396" t="inlineStr"/>
@@ -10550,14 +10550,14 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>1290</v>
+        <v>1301</v>
       </c>
       <c r="B397" t="n">
         <v>2</v>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Xin Run 20</t>
+          <t>Yicheng27</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -10575,7 +10575,7 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>1298</v>
+        <v>1303</v>
       </c>
       <c r="B398" t="n">
         <v>2</v>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Hai Hang You 7</t>
+          <t>Hongheng189</t>
         </is>
       </c>
       <c r="E398" t="inlineStr"/>
@@ -10600,19 +10600,19 @@
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>1300</v>
+        <v>1307</v>
       </c>
       <c r="B399" t="n">
         <v>2</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Hui Chen 118</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
+          <t>Jin Shi 77</t>
         </is>
       </c>
       <c r="E399" t="inlineStr"/>
@@ -10625,19 +10625,19 @@
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>1301</v>
+        <v>1308</v>
       </c>
       <c r="B400" t="n">
         <v>2</v>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Yicheng27</t>
+          <t>Chaoyang301</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Chao Yang 302</t>
         </is>
       </c>
       <c r="E400" t="inlineStr"/>
@@ -10650,22 +10650,26 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>1303</v>
+        <v>1309</v>
       </c>
       <c r="B401" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Hongheng189</t>
-        </is>
-      </c>
-      <c r="E401" t="inlineStr"/>
+          <t>Heng Xing 9</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Dong Gang You66</t>
+        </is>
+      </c>
       <c r="F401" t="inlineStr"/>
       <c r="G401" t="inlineStr"/>
       <c r="H401" t="inlineStr"/>
@@ -10675,19 +10679,19 @@
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>1307</v>
+        <v>1312</v>
       </c>
       <c r="B402" t="n">
         <v>2</v>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Hui Chen 118</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Jin Shi 77</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="E402" t="inlineStr"/>
@@ -10700,19 +10704,19 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>1308</v>
+        <v>1322</v>
       </c>
       <c r="B403" t="n">
         <v>2</v>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Chaoyang301</t>
+          <t>Dong Sheng You 77</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Chao Yang 302</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="E403" t="inlineStr"/>
@@ -10725,14 +10729,14 @@
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>1309</v>
+        <v>1336</v>
       </c>
       <c r="B404" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Yicheng27</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -10740,11 +10744,7 @@
           <t>Dong Gang You66</t>
         </is>
       </c>
-      <c r="E404" t="inlineStr">
-        <is>
-          <t>Heng Xing 9</t>
-        </is>
-      </c>
+      <c r="E404" t="inlineStr"/>
       <c r="F404" t="inlineStr"/>
       <c r="G404" t="inlineStr"/>
       <c r="H404" t="inlineStr"/>
@@ -10754,19 +10754,19 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>1312</v>
+        <v>1337</v>
       </c>
       <c r="B405" t="n">
         <v>2</v>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Hua Ran 177</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="E405" t="inlineStr"/>
@@ -10779,22 +10779,26 @@
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>1322</v>
+        <v>1339</v>
       </c>
       <c r="B406" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Run Ji 17</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Dong Sheng You 77</t>
-        </is>
-      </c>
-      <c r="E406" t="inlineStr"/>
+          <t>Yong Cheng 97</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Yong Cheng 97</t>
+        </is>
+      </c>
       <c r="F406" t="inlineStr"/>
       <c r="G406" t="inlineStr"/>
       <c r="H406" t="inlineStr"/>
@@ -10804,14 +10808,14 @@
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>1336</v>
+        <v>1349</v>
       </c>
       <c r="B407" t="n">
         <v>2</v>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Yicheng27</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -10829,22 +10833,26 @@
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>1337</v>
+        <v>1352</v>
       </c>
       <c r="B408" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Hua Ran 177</t>
+          <t>Xin Sheng 17</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
-        </is>
-      </c>
-      <c r="E408" t="inlineStr"/>
+          <t>Xin Sheng 17</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Dong Gang You66</t>
+        </is>
+      </c>
       <c r="F408" t="inlineStr"/>
       <c r="G408" t="inlineStr"/>
       <c r="H408" t="inlineStr"/>
@@ -10854,26 +10862,22 @@
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>1339</v>
+        <v>1353</v>
       </c>
       <c r="B409" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Run Ji 17</t>
+          <t>Yicheng27</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Yong Cheng 97</t>
-        </is>
-      </c>
-      <c r="E409" t="inlineStr">
-        <is>
-          <t>Yong Cheng 97</t>
-        </is>
-      </c>
+          <t>Dong Gang You66</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr"/>
       <c r="F409" t="inlineStr"/>
       <c r="G409" t="inlineStr"/>
       <c r="H409" t="inlineStr"/>
@@ -10883,19 +10887,19 @@
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>1349</v>
+        <v>1356</v>
       </c>
       <c r="B410" t="n">
         <v>2</v>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Yuanxiangyou16</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="E410" t="inlineStr"/>
@@ -10908,26 +10912,22 @@
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>1352</v>
+        <v>1362</v>
       </c>
       <c r="B411" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Xin Sheng 17</t>
+          <t>Ning Feng You 1</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Xin Sheng 17</t>
-        </is>
-      </c>
-      <c r="E411" t="inlineStr">
-        <is>
           <t>Dong Gang You66</t>
         </is>
       </c>
+      <c r="E411" t="inlineStr"/>
       <c r="F411" t="inlineStr"/>
       <c r="G411" t="inlineStr"/>
       <c r="H411" t="inlineStr"/>
@@ -10937,7 +10937,7 @@
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>1353</v>
+        <v>1363</v>
       </c>
       <c r="B412" t="n">
         <v>2</v>
@@ -10962,22 +10962,26 @@
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>1356</v>
+        <v>1366</v>
       </c>
       <c r="B413" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Yuanxiangyou16</t>
+          <t>Long Yu 18</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
-        </is>
-      </c>
-      <c r="E413" t="inlineStr"/>
+          <t>Yiding6</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Yiding6</t>
+        </is>
+      </c>
       <c r="F413" t="inlineStr"/>
       <c r="G413" t="inlineStr"/>
       <c r="H413" t="inlineStr"/>
@@ -10987,14 +10991,14 @@
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>1362</v>
+        <v>1368</v>
       </c>
       <c r="B414" t="n">
         <v>2</v>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Ning Feng You 1</t>
+          <t>Yicheng27</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -11012,19 +11016,19 @@
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>1363</v>
+        <v>1369</v>
       </c>
       <c r="B415" t="n">
         <v>2</v>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Yicheng27</t>
+          <t>Hongheng169</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Zhoushun5</t>
         </is>
       </c>
       <c r="E415" t="inlineStr"/>
@@ -11037,26 +11041,22 @@
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>1366</v>
+        <v>1370</v>
       </c>
       <c r="B416" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Long Yu 18</t>
+          <t>Hong Da Hai 88</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Yiding6</t>
-        </is>
-      </c>
-      <c r="E416" t="inlineStr">
-        <is>
-          <t>Yiding6</t>
-        </is>
-      </c>
+          <t>Dong Gang You66</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr"/>
       <c r="F416" t="inlineStr"/>
       <c r="G416" t="inlineStr"/>
       <c r="H416" t="inlineStr"/>
@@ -11066,7 +11066,7 @@
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>1368</v>
+        <v>1371</v>
       </c>
       <c r="B417" t="n">
         <v>2</v>
@@ -11091,19 +11091,19 @@
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>1369</v>
+        <v>1375</v>
       </c>
       <c r="B418" t="n">
         <v>2</v>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Shun Ping 17</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Zhoushun5</t>
+          <t>Xin Sheng 17</t>
         </is>
       </c>
       <c r="E418" t="inlineStr"/>
@@ -11116,19 +11116,19 @@
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>1370</v>
+        <v>1377</v>
       </c>
       <c r="B419" t="n">
         <v>2</v>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Hong Da Hai 88</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Yong Cheng 166</t>
         </is>
       </c>
       <c r="E419" t="inlineStr"/>
@@ -11141,19 +11141,19 @@
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>1371</v>
+        <v>1378</v>
       </c>
       <c r="B420" t="n">
         <v>2</v>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Yicheng27</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Huaran166</t>
         </is>
       </c>
       <c r="E420" t="inlineStr"/>
@@ -11166,19 +11166,19 @@
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>1375</v>
+        <v>1395</v>
       </c>
       <c r="B421" t="n">
         <v>2</v>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Shun Ping 17</t>
+          <t>Hai Xiang 5</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Xin Sheng 17</t>
+          <t>Hai Xiang 5</t>
         </is>
       </c>
       <c r="E421" t="inlineStr"/>
@@ -11191,19 +11191,19 @@
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>1377</v>
+        <v>1399</v>
       </c>
       <c r="B422" t="n">
         <v>2</v>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Fu Jie 168</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Yong Cheng 166</t>
+          <t>Ning Feng Xing Chen</t>
         </is>
       </c>
       <c r="E422" t="inlineStr"/>
@@ -11216,19 +11216,19 @@
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>1378</v>
+        <v>1401</v>
       </c>
       <c r="B423" t="n">
         <v>2</v>
       </c>
       <c r="C423" t="inlineStr">
         <is>
+          <t>Heng Xing 9</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
           <t>Dong Gang You66</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>Huaran166</t>
         </is>
       </c>
       <c r="E423" t="inlineStr"/>
@@ -11241,44 +11241,60 @@
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>1395</v>
+        <v>1406</v>
       </c>
       <c r="B424" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Hai Xiang 5</t>
+          <t>Xin Shi Ji 7</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Hai Xiang 5</t>
-        </is>
-      </c>
-      <c r="E424" t="inlineStr"/>
-      <c r="F424" t="inlineStr"/>
-      <c r="G424" t="inlineStr"/>
-      <c r="H424" t="inlineStr"/>
+          <t>Zhong Fan 323</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Zhongdayou288</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Zhong Fan 323</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>Zhongdayou288</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>Zhong Fan 323</t>
+        </is>
+      </c>
       <c r="I424" t="inlineStr"/>
       <c r="J424" t="inlineStr"/>
       <c r="K424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>1399</v>
+        <v>1408</v>
       </c>
       <c r="B425" t="n">
         <v>2</v>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Fu Jie 168</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Ning Feng Xing Chen</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="E425" t="inlineStr"/>
@@ -11291,19 +11307,19 @@
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>1401</v>
+        <v>1412</v>
       </c>
       <c r="B426" t="n">
         <v>2</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Chao Yang302</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Chao Yang302</t>
         </is>
       </c>
       <c r="E426" t="inlineStr"/>
@@ -11316,48 +11332,36 @@
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>1406</v>
+        <v>1420</v>
       </c>
       <c r="B427" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Xin Shi Ji 7</t>
+          <t>Dong Sheng You 77</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Zhong Fan 323</t>
+          <t>Shun Ping 19</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Zhongdayou288</t>
-        </is>
-      </c>
-      <c r="F427" t="inlineStr">
-        <is>
-          <t>Zhong Fan 323</t>
-        </is>
-      </c>
-      <c r="G427" t="inlineStr">
-        <is>
-          <t>Zhongdayou288</t>
-        </is>
-      </c>
-      <c r="H427" t="inlineStr">
-        <is>
-          <t>Zhong Fan 323</t>
-        </is>
-      </c>
+          <t>Shun Ping 19</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr"/>
+      <c r="G427" t="inlineStr"/>
+      <c r="H427" t="inlineStr"/>
       <c r="I427" t="inlineStr"/>
       <c r="J427" t="inlineStr"/>
       <c r="K427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>1408</v>
+        <v>1422</v>
       </c>
       <c r="B428" t="n">
         <v>2</v>
@@ -11382,19 +11386,19 @@
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>1412</v>
+        <v>1430</v>
       </c>
       <c r="B429" t="n">
         <v>2</v>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Chao Yang302</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Chao Yang302</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="E429" t="inlineStr"/>
@@ -11407,26 +11411,22 @@
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>1420</v>
+        <v>1434</v>
       </c>
       <c r="B430" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Dong Sheng You 77</t>
+          <t>Si Jie 21</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Shun Ping 19</t>
-        </is>
-      </c>
-      <c r="E430" t="inlineStr">
-        <is>
-          <t>Shun Ping 19</t>
-        </is>
-      </c>
+          <t>Si Jie 21</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr"/>
       <c r="F430" t="inlineStr"/>
       <c r="G430" t="inlineStr"/>
       <c r="H430" t="inlineStr"/>
@@ -11436,44 +11436,72 @@
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>1422</v>
+        <v>1439</v>
       </c>
       <c r="B431" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Bai Da 28</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
-        </is>
-      </c>
-      <c r="E431" t="inlineStr"/>
-      <c r="F431" t="inlineStr"/>
-      <c r="G431" t="inlineStr"/>
-      <c r="H431" t="inlineStr"/>
-      <c r="I431" t="inlineStr"/>
-      <c r="J431" t="inlineStr"/>
-      <c r="K431" t="inlineStr"/>
+          <t>Hai Hang You 7</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Jin Shi 77</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Bai Da 28</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>Hai Hang You 7</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>Jin Shi 77</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>Zhou Hai Qing 1</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>Zhouhaiqing16</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Zhouhaiqing16</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>1430</v>
+        <v>1443</v>
       </c>
       <c r="B432" t="n">
         <v>2</v>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Jin Hui 17</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Jin Hui 17</t>
         </is>
       </c>
       <c r="E432" t="inlineStr"/>
@@ -11486,19 +11514,19 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>1434</v>
+        <v>1452</v>
       </c>
       <c r="B433" t="n">
         <v>2</v>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Si Jie 21</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Si Jie 21</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="E433" t="inlineStr"/>
@@ -11511,72 +11539,48 @@
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>1439</v>
+        <v>1454</v>
       </c>
       <c r="B434" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Bai Da 28</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Hai Hang You 7</t>
+          <t>Xin Kai 1</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Jin Shi 77</t>
-        </is>
-      </c>
-      <c r="F434" t="inlineStr">
-        <is>
-          <t>Hai Hang You 7</t>
-        </is>
-      </c>
-      <c r="G434" t="inlineStr">
-        <is>
-          <t>Bai Da 28</t>
-        </is>
-      </c>
-      <c r="H434" t="inlineStr">
-        <is>
-          <t>Jin Shi 77</t>
-        </is>
-      </c>
-      <c r="I434" t="inlineStr">
-        <is>
-          <t>Zhou Hai Qing 1</t>
-        </is>
-      </c>
-      <c r="J434" t="inlineStr">
-        <is>
-          <t>Zhouhaiqing16</t>
-        </is>
-      </c>
-      <c r="K434" t="inlineStr">
-        <is>
-          <t>Zhouhaiqing16</t>
-        </is>
-      </c>
+          <t>Dong Gang You66</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" t="inlineStr"/>
+      <c r="H434" t="inlineStr"/>
+      <c r="I434" t="inlineStr"/>
+      <c r="J434" t="inlineStr"/>
+      <c r="K434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>1443</v>
+        <v>1455</v>
       </c>
       <c r="B435" t="n">
         <v>2</v>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Jin Hui 17</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Jin Hui 17</t>
+          <t>Dong Sheng You 77</t>
         </is>
       </c>
       <c r="E435" t="inlineStr"/>
@@ -11589,19 +11593,19 @@
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>1452</v>
+        <v>1462</v>
       </c>
       <c r="B436" t="n">
         <v>2</v>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Hongheng169</t>
         </is>
       </c>
       <c r="E436" t="inlineStr"/>
@@ -11614,26 +11618,22 @@
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>1454</v>
+        <v>1467</v>
       </c>
       <c r="B437" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C437" t="inlineStr">
         <is>
+          <t>Heng Xing 9</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
           <t>Dong Gang You66</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>Xin Kai 1</t>
-        </is>
-      </c>
-      <c r="E437" t="inlineStr">
-        <is>
-          <t>Dong Gang You66</t>
-        </is>
-      </c>
+      <c r="E437" t="inlineStr"/>
       <c r="F437" t="inlineStr"/>
       <c r="G437" t="inlineStr"/>
       <c r="H437" t="inlineStr"/>
@@ -11643,19 +11643,19 @@
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>1455</v>
+        <v>1475</v>
       </c>
       <c r="B438" t="n">
         <v>2</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Hui Chen 118</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Dong Sheng You 77</t>
+          <t>Jin Hui 17</t>
         </is>
       </c>
       <c r="E438" t="inlineStr"/>
@@ -11668,19 +11668,19 @@
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>1462</v>
+        <v>1476</v>
       </c>
       <c r="B439" t="n">
         <v>2</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Shun Ping 17</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Kang--Fa--125</t>
         </is>
       </c>
       <c r="E439" t="inlineStr"/>
@@ -11693,22 +11693,26 @@
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>1467</v>
+        <v>1479</v>
       </c>
       <c r="B440" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
-        </is>
-      </c>
-      <c r="E440" t="inlineStr"/>
+          <t>Hua Ran 177</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Hongheng169</t>
+        </is>
+      </c>
       <c r="F440" t="inlineStr"/>
       <c r="G440" t="inlineStr"/>
       <c r="H440" t="inlineStr"/>
@@ -11718,19 +11722,19 @@
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>1472</v>
+        <v>1481</v>
       </c>
       <c r="B441" t="n">
         <v>2</v>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Chaoyang301</t>
+          <t>Hai Xiang 5</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Fu Jie 168</t>
+          <t>Hui Chen 118</t>
         </is>
       </c>
       <c r="E441" t="inlineStr"/>
@@ -11743,19 +11747,19 @@
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>1473</v>
+        <v>1482</v>
       </c>
       <c r="B442" t="n">
         <v>2</v>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Xin Ke 16</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>An Tong 27</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="E442" t="inlineStr"/>
@@ -11768,19 +11772,19 @@
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>1475</v>
+        <v>1486</v>
       </c>
       <c r="B443" t="n">
         <v>2</v>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Hui Chen 118</t>
+          <t>Hongheng169</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Jin Hui 17</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="E443" t="inlineStr"/>
@@ -11793,19 +11797,19 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>1476</v>
+        <v>1491</v>
       </c>
       <c r="B444" t="n">
         <v>2</v>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Shun Ping 17</t>
+          <t>Zhong Fan 323</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Kang--Fa--125</t>
+          <t>Jin Se Hai Yang 20</t>
         </is>
       </c>
       <c r="E444" t="inlineStr"/>
@@ -11818,26 +11822,22 @@
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>1479</v>
+        <v>1495</v>
       </c>
       <c r="B445" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C445" t="inlineStr">
         <is>
+          <t>Heng Xing 9</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
           <t>Dong Gang You66</t>
         </is>
       </c>
-      <c r="D445" t="inlineStr">
-        <is>
-          <t>Hua Ran 177</t>
-        </is>
-      </c>
-      <c r="E445" t="inlineStr">
-        <is>
-          <t>Hongheng169</t>
-        </is>
-      </c>
+      <c r="E445" t="inlineStr"/>
       <c r="F445" t="inlineStr"/>
       <c r="G445" t="inlineStr"/>
       <c r="H445" t="inlineStr"/>
@@ -11847,19 +11847,19 @@
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>1481</v>
+        <v>1499</v>
       </c>
       <c r="B446" t="n">
         <v>2</v>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Hai Xiang 5</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Hui Chen 118</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="E446" t="inlineStr"/>
@@ -11872,14 +11872,14 @@
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>1482</v>
+        <v>1504</v>
       </c>
       <c r="B447" t="n">
         <v>2</v>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Xin Ke 16</t>
+          <t>Hongheng169</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -11897,14 +11897,14 @@
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>1486</v>
+        <v>1513</v>
       </c>
       <c r="B448" t="n">
         <v>2</v>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -11922,19 +11922,19 @@
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>1491</v>
+        <v>1516</v>
       </c>
       <c r="B449" t="n">
         <v>2</v>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Zhong Fan 323</t>
+          <t>Zhou Da You 7</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Jin Se Hai Yang 20</t>
+          <t>Hai Xiang 17</t>
         </is>
       </c>
       <c r="E449" t="inlineStr"/>
@@ -11947,19 +11947,19 @@
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>1495</v>
+        <v>1517</v>
       </c>
       <c r="B450" t="n">
         <v>2</v>
       </c>
       <c r="C450" t="inlineStr">
         <is>
+          <t>Zhong Xing You 6</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
           <t>Heng Xing 9</t>
-        </is>
-      </c>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="E450" t="inlineStr"/>
@@ -11972,19 +11972,19 @@
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>1499</v>
+        <v>1521</v>
       </c>
       <c r="B451" t="n">
         <v>2</v>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Yicheng27</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Le Yang 1</t>
         </is>
       </c>
       <c r="E451" t="inlineStr"/>
@@ -11997,19 +11997,19 @@
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>1503</v>
+        <v>1527</v>
       </c>
       <c r="B452" t="n">
         <v>2</v>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Zhou Shun 10</t>
+          <t>Le Yang 1</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Yicheng27</t>
         </is>
       </c>
       <c r="E452" t="inlineStr"/>
@@ -12022,19 +12022,19 @@
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>1504</v>
+        <v>1530</v>
       </c>
       <c r="B453" t="n">
         <v>2</v>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Le Yang 1</t>
         </is>
       </c>
       <c r="E453" t="inlineStr"/>
@@ -12047,19 +12047,19 @@
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>1513</v>
+        <v>1531</v>
       </c>
       <c r="B454" t="n">
         <v>2</v>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Le Yang 1</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Yicheng27</t>
         </is>
       </c>
       <c r="E454" t="inlineStr"/>
@@ -12072,19 +12072,19 @@
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>1516</v>
+        <v>1536</v>
       </c>
       <c r="B455" t="n">
         <v>2</v>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Zhou Da You 7</t>
+          <t>Zhe Hai You 5</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Hai Xiang 17</t>
+          <t>Run Ze 11</t>
         </is>
       </c>
       <c r="E455" t="inlineStr"/>
@@ -12097,19 +12097,19 @@
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>1517</v>
+        <v>1539</v>
       </c>
       <c r="B456" t="n">
         <v>2</v>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Zhong Xing You 6</t>
+          <t>Chaoyang301</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Le Yang 1</t>
         </is>
       </c>
       <c r="E456" t="inlineStr"/>
@@ -12122,14 +12122,14 @@
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>1521</v>
+        <v>1543</v>
       </c>
       <c r="B457" t="n">
         <v>2</v>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Yicheng27</t>
+          <t>Xin Kai 1</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -12147,19 +12147,19 @@
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>1527</v>
+        <v>1550</v>
       </c>
       <c r="B458" t="n">
         <v>2</v>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Le Yang 1</t>
+          <t>Shen Jia 9</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Yicheng27</t>
+          <t>Jin Hui 17</t>
         </is>
       </c>
       <c r="E458" t="inlineStr"/>
@@ -12172,19 +12172,19 @@
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>1530</v>
+        <v>1553</v>
       </c>
       <c r="B459" t="n">
         <v>2</v>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Bo Hai Gong 7</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Le Yang 1</t>
+          <t>Bo Hai Gong 7</t>
         </is>
       </c>
       <c r="E459" t="inlineStr"/>
@@ -12197,19 +12197,19 @@
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>1531</v>
+        <v>1556</v>
       </c>
       <c r="B460" t="n">
         <v>2</v>
       </c>
       <c r="C460" t="inlineStr">
         <is>
+          <t>Heng Xing 9</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
           <t>Le Yang 1</t>
-        </is>
-      </c>
-      <c r="D460" t="inlineStr">
-        <is>
-          <t>Yicheng27</t>
         </is>
       </c>
       <c r="E460" t="inlineStr"/>
@@ -12222,19 +12222,19 @@
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>1536</v>
+        <v>1558</v>
       </c>
       <c r="B461" t="n">
         <v>2</v>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Zhe Hai You 5</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Run Ze 11</t>
+          <t>Le Yang 1</t>
         </is>
       </c>
       <c r="E461" t="inlineStr"/>
@@ -12247,14 +12247,14 @@
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>1539</v>
+        <v>1559</v>
       </c>
       <c r="B462" t="n">
         <v>2</v>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Chaoyang301</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -12272,14 +12272,14 @@
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>1543</v>
+        <v>1565</v>
       </c>
       <c r="B463" t="n">
         <v>2</v>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Xin Kai 1</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -12297,19 +12297,19 @@
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>1550</v>
+        <v>1572</v>
       </c>
       <c r="B464" t="n">
         <v>2</v>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Shen Jia 9</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Jin Hui 17</t>
+          <t>Yi Shun 11</t>
         </is>
       </c>
       <c r="E464" t="inlineStr"/>
@@ -12322,19 +12322,19 @@
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>1553</v>
+        <v>1573</v>
       </c>
       <c r="B465" t="n">
         <v>2</v>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Bo Hai Gong 7</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>Bo Hai Gong 7</t>
+          <t>Le Yang 1</t>
         </is>
       </c>
       <c r="E465" t="inlineStr"/>
@@ -12347,19 +12347,19 @@
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>1556</v>
+        <v>1576</v>
       </c>
       <c r="B466" t="n">
         <v>2</v>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Yicheng27</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Le Yang 1</t>
+          <t>Yi Shun 11</t>
         </is>
       </c>
       <c r="E466" t="inlineStr"/>
@@ -12372,7 +12372,7 @@
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>1558</v>
+        <v>1577</v>
       </c>
       <c r="B467" t="n">
         <v>2</v>
@@ -12397,19 +12397,19 @@
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>1559</v>
+        <v>1585</v>
       </c>
       <c r="B468" t="n">
         <v>2</v>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Le Yang 1</t>
+          <t>Ming Feng 7</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Ming Feng 7</t>
         </is>
       </c>
       <c r="E468" t="inlineStr"/>
@@ -12422,14 +12422,14 @@
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>1565</v>
+        <v>1594</v>
       </c>
       <c r="B469" t="n">
         <v>2</v>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Hai Zhi Run 69</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -12447,19 +12447,19 @@
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>1572</v>
+        <v>1597</v>
       </c>
       <c r="B470" t="n">
         <v>2</v>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Hongheng189</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Yi Shun 11</t>
+          <t>Le Yang 1</t>
         </is>
       </c>
       <c r="E470" t="inlineStr"/>
@@ -12472,14 +12472,14 @@
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>1573</v>
+        <v>1603</v>
       </c>
       <c r="B471" t="n">
         <v>2</v>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Hongheng169</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -12497,19 +12497,19 @@
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>1576</v>
+        <v>1605</v>
       </c>
       <c r="B472" t="n">
         <v>2</v>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Yicheng27</t>
+          <t>Hongheng169</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Yi Shun 11</t>
+          <t>Le Yang 1</t>
         </is>
       </c>
       <c r="E472" t="inlineStr"/>
@@ -12522,19 +12522,19 @@
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>1577</v>
+        <v>1617</v>
       </c>
       <c r="B473" t="n">
         <v>2</v>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Run Ji 17</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Le Yang 1</t>
+          <t>Yong Cheng 97</t>
         </is>
       </c>
       <c r="E473" t="inlineStr"/>
@@ -12547,19 +12547,19 @@
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>1585</v>
+        <v>1618</v>
       </c>
       <c r="B474" t="n">
         <v>2</v>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Ming Feng 7</t>
+          <t>Le Yang 1</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Ming Feng 7</t>
+          <t>Le Yang 1</t>
         </is>
       </c>
       <c r="E474" t="inlineStr"/>
@@ -12572,14 +12572,14 @@
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>1594</v>
+        <v>1621</v>
       </c>
       <c r="B475" t="n">
         <v>2</v>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Hai Zhi Run 69</t>
+          <t>Hongheng169</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -12597,14 +12597,14 @@
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>1597</v>
+        <v>1622</v>
       </c>
       <c r="B476" t="n">
         <v>2</v>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Hongheng189</t>
+          <t>Le Yang 1</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -12622,19 +12622,19 @@
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>1603</v>
+        <v>1623</v>
       </c>
       <c r="B477" t="n">
         <v>2</v>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Run Ji 17</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Le Yang 1</t>
+          <t>Hua Guang 68</t>
         </is>
       </c>
       <c r="E477" t="inlineStr"/>
@@ -12647,19 +12647,19 @@
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>1605</v>
+        <v>1627</v>
       </c>
       <c r="B478" t="n">
         <v>2</v>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Hua Guang 68</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Le Yang 1</t>
+          <t>Run Ji 17</t>
         </is>
       </c>
       <c r="E478" t="inlineStr"/>
@@ -12672,19 +12672,19 @@
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>1617</v>
+        <v>1632</v>
       </c>
       <c r="B479" t="n">
         <v>2</v>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Run Ji 17</t>
+          <t>Fu Jie 168</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Yong Cheng 97</t>
+          <t>Chao Yang 302</t>
         </is>
       </c>
       <c r="E479" t="inlineStr"/>
@@ -12697,19 +12697,19 @@
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>1618</v>
+        <v>1636</v>
       </c>
       <c r="B480" t="n">
         <v>2</v>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Le Yang 1</t>
+          <t>Hai Hang You 7</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Le Yang 1</t>
+          <t>Zhongdayou288</t>
         </is>
       </c>
       <c r="E480" t="inlineStr"/>
@@ -12722,22 +12722,26 @@
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>1621</v>
+        <v>1637</v>
       </c>
       <c r="B481" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Zhongdayou288</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Le Yang 1</t>
-        </is>
-      </c>
-      <c r="E481" t="inlineStr"/>
+          <t>Jin Shi 77</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>Fu Jie 168</t>
+        </is>
+      </c>
       <c r="F481" t="inlineStr"/>
       <c r="G481" t="inlineStr"/>
       <c r="H481" t="inlineStr"/>
@@ -12745,160 +12749,6 @@
       <c r="J481" t="inlineStr"/>
       <c r="K481" t="inlineStr"/>
     </row>
-    <row r="482">
-      <c r="A482" t="n">
-        <v>1622</v>
-      </c>
-      <c r="B482" t="n">
-        <v>2</v>
-      </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>Le Yang 1</t>
-        </is>
-      </c>
-      <c r="D482" t="inlineStr">
-        <is>
-          <t>Le Yang 1</t>
-        </is>
-      </c>
-      <c r="E482" t="inlineStr"/>
-      <c r="F482" t="inlineStr"/>
-      <c r="G482" t="inlineStr"/>
-      <c r="H482" t="inlineStr"/>
-      <c r="I482" t="inlineStr"/>
-      <c r="J482" t="inlineStr"/>
-      <c r="K482" t="inlineStr"/>
-    </row>
-    <row r="483">
-      <c r="A483" t="n">
-        <v>1623</v>
-      </c>
-      <c r="B483" t="n">
-        <v>2</v>
-      </c>
-      <c r="C483" t="inlineStr">
-        <is>
-          <t>Run Ji 17</t>
-        </is>
-      </c>
-      <c r="D483" t="inlineStr">
-        <is>
-          <t>Hua Guang 68</t>
-        </is>
-      </c>
-      <c r="E483" t="inlineStr"/>
-      <c r="F483" t="inlineStr"/>
-      <c r="G483" t="inlineStr"/>
-      <c r="H483" t="inlineStr"/>
-      <c r="I483" t="inlineStr"/>
-      <c r="J483" t="inlineStr"/>
-      <c r="K483" t="inlineStr"/>
-    </row>
-    <row r="484">
-      <c r="A484" t="n">
-        <v>1627</v>
-      </c>
-      <c r="B484" t="n">
-        <v>2</v>
-      </c>
-      <c r="C484" t="inlineStr">
-        <is>
-          <t>Hua Guang 68</t>
-        </is>
-      </c>
-      <c r="D484" t="inlineStr">
-        <is>
-          <t>Run Ji 17</t>
-        </is>
-      </c>
-      <c r="E484" t="inlineStr"/>
-      <c r="F484" t="inlineStr"/>
-      <c r="G484" t="inlineStr"/>
-      <c r="H484" t="inlineStr"/>
-      <c r="I484" t="inlineStr"/>
-      <c r="J484" t="inlineStr"/>
-      <c r="K484" t="inlineStr"/>
-    </row>
-    <row r="485">
-      <c r="A485" t="n">
-        <v>1632</v>
-      </c>
-      <c r="B485" t="n">
-        <v>2</v>
-      </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>Fu Jie 168</t>
-        </is>
-      </c>
-      <c r="D485" t="inlineStr">
-        <is>
-          <t>Chao Yang 302</t>
-        </is>
-      </c>
-      <c r="E485" t="inlineStr"/>
-      <c r="F485" t="inlineStr"/>
-      <c r="G485" t="inlineStr"/>
-      <c r="H485" t="inlineStr"/>
-      <c r="I485" t="inlineStr"/>
-      <c r="J485" t="inlineStr"/>
-      <c r="K485" t="inlineStr"/>
-    </row>
-    <row r="486">
-      <c r="A486" t="n">
-        <v>1636</v>
-      </c>
-      <c r="B486" t="n">
-        <v>2</v>
-      </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>Zhongdayou288</t>
-        </is>
-      </c>
-      <c r="D486" t="inlineStr">
-        <is>
-          <t>Hai Hang You 7</t>
-        </is>
-      </c>
-      <c r="E486" t="inlineStr"/>
-      <c r="F486" t="inlineStr"/>
-      <c r="G486" t="inlineStr"/>
-      <c r="H486" t="inlineStr"/>
-      <c r="I486" t="inlineStr"/>
-      <c r="J486" t="inlineStr"/>
-      <c r="K486" t="inlineStr"/>
-    </row>
-    <row r="487">
-      <c r="A487" t="n">
-        <v>1637</v>
-      </c>
-      <c r="B487" t="n">
-        <v>3</v>
-      </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>Zhongdayou288</t>
-        </is>
-      </c>
-      <c r="D487" t="inlineStr">
-        <is>
-          <t>Jin Shi 77</t>
-        </is>
-      </c>
-      <c r="E487" t="inlineStr">
-        <is>
-          <t>Fu Jie 168</t>
-        </is>
-      </c>
-      <c r="F487" t="inlineStr"/>
-      <c r="G487" t="inlineStr"/>
-      <c r="H487" t="inlineStr"/>
-      <c r="I487" t="inlineStr"/>
-      <c r="J487" t="inlineStr"/>
-      <c r="K487" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/multi_sts_cases.xlsx
+++ b/logs/multi_sts_cases.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K487"/>
+  <dimension ref="A1:K481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9121,19 +9121,19 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="B340" t="n">
         <v>2</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Hui Chen 118</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Shun Ping 17</t>
         </is>
       </c>
       <c r="E340" t="inlineStr"/>
@@ -9146,19 +9146,19 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>1139</v>
+        <v>1145</v>
       </c>
       <c r="B341" t="n">
         <v>2</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
+          <t>Shun Ping 17</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
           <t>Yuan Xiang You 16</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>Shun Ping 17</t>
         </is>
       </c>
       <c r="E341" t="inlineStr"/>
@@ -9171,19 +9171,19 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>1145</v>
+        <v>1151</v>
       </c>
       <c r="B342" t="n">
         <v>2</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
+          <t>Yuan Xiang You 16</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
           <t>Shun Ping 17</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E342" t="inlineStr"/>
@@ -9196,19 +9196,19 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="B343" t="n">
         <v>2</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
+          <t>Yuan Xiang You 16</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
           <t>Shun Ping 17</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E343" t="inlineStr"/>
@@ -9221,7 +9221,7 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>1151</v>
+        <v>1161</v>
       </c>
       <c r="B344" t="n">
         <v>2</v>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Shun Ping 17</t>
+          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="E344" t="inlineStr"/>
@@ -9246,19 +9246,19 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>1152</v>
+        <v>1163</v>
       </c>
       <c r="B345" t="n">
         <v>2</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
+          <t>Tian Sheng You 19</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
           <t>Yuan Xiang You 16</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>Shun Ping 17</t>
         </is>
       </c>
       <c r="E345" t="inlineStr"/>
@@ -9271,19 +9271,19 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="B346" t="n">
         <v>2</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
+          <t>Shun Ping 17</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
           <t>Yuan Xiang You 16</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="E346" t="inlineStr"/>
@@ -9296,19 +9296,19 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>1163</v>
+        <v>1169</v>
       </c>
       <c r="B347" t="n">
         <v>2</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
+          <t>Yuan Xiang You 16</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
           <t>Tian Sheng You 19</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E347" t="inlineStr"/>
@@ -9321,14 +9321,14 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>1164</v>
+        <v>1170</v>
       </c>
       <c r="B348" t="n">
         <v>2</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Shun Ping 17</t>
+          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -9346,19 +9346,19 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="B349" t="n">
         <v>2</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Hongheng169</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
+          <t>Shun Kai 7</t>
         </is>
       </c>
       <c r="E349" t="inlineStr"/>
@@ -9371,19 +9371,19 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="B350" t="n">
         <v>2</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
+          <t>Yuan Xiang You 16</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
           <t>Tian Sheng You 19</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E350" t="inlineStr"/>
@@ -9396,19 +9396,19 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B351" t="n">
         <v>2</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Shun Kai 7</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E351" t="inlineStr"/>
@@ -9421,19 +9421,19 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="B352" t="n">
         <v>2</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Yicheng27</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="E352" t="inlineStr"/>
@@ -9446,19 +9446,19 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>1174</v>
+        <v>1177</v>
       </c>
       <c r="B353" t="n">
         <v>2</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
+          <t>Yuan Xiang You 16</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
           <t>Tian Sheng You 19</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E353" t="inlineStr"/>
@@ -9471,19 +9471,19 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="B354" t="n">
         <v>2</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Yicheng27</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Hongheng169</t>
         </is>
       </c>
       <c r="E354" t="inlineStr"/>
@@ -9496,7 +9496,7 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="B355" t="n">
         <v>2</v>
@@ -9521,19 +9521,19 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>1178</v>
+        <v>1182</v>
       </c>
       <c r="B356" t="n">
         <v>2</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Zhoushun5</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Zhoushun5</t>
         </is>
       </c>
       <c r="E356" t="inlineStr"/>
@@ -9546,19 +9546,19 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>1179</v>
+        <v>1183</v>
       </c>
       <c r="B357" t="n">
         <v>2</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Xin Ke 16</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
+          <t>Xin Ke 16</t>
         </is>
       </c>
       <c r="E357" t="inlineStr"/>
@@ -9571,19 +9571,19 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="B358" t="n">
         <v>2</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Zhoushun5</t>
+          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Zhoushun5</t>
+          <t>Zhe Hai You 5</t>
         </is>
       </c>
       <c r="E358" t="inlineStr"/>
@@ -9596,19 +9596,19 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>1183</v>
+        <v>1187</v>
       </c>
       <c r="B359" t="n">
         <v>2</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Xin Ke 16</t>
+          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Xin Ke 16</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E359" t="inlineStr"/>
@@ -9621,7 +9621,7 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>1184</v>
+        <v>1190</v>
       </c>
       <c r="B360" t="n">
         <v>2</v>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Zhe Hai You 5</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E360" t="inlineStr"/>
@@ -9646,14 +9646,14 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>1187</v>
+        <v>1196</v>
       </c>
       <c r="B361" t="n">
         <v>2</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -9671,22 +9671,26 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>1190</v>
+        <v>1201</v>
       </c>
       <c r="B362" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
+          <t>Hai Xiang 17</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
+          <t>Hai Xiang 17</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
           <t>Yuan Xiang You 16</t>
         </is>
       </c>
-      <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr"/>
       <c r="G362" t="inlineStr"/>
       <c r="H362" t="inlineStr"/>
@@ -9696,19 +9700,19 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>1196</v>
+        <v>1206</v>
       </c>
       <c r="B363" t="n">
         <v>2</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
+          <t>Hongheng169</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
           <t>Heng Xing 9</t>
-        </is>
-      </c>
-      <c r="D363" t="inlineStr">
-        <is>
-          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E363" t="inlineStr"/>
@@ -9721,26 +9725,22 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>1201</v>
+        <v>1207</v>
       </c>
       <c r="B364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Hai Xiang 17</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Hai Xiang 17</t>
-        </is>
-      </c>
-      <c r="E364" t="inlineStr">
-        <is>
-          <t>Yuan Xiang You 16</t>
-        </is>
-      </c>
+          <t>Tian Sheng You 19</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr"/>
       <c r="G364" t="inlineStr"/>
       <c r="H364" t="inlineStr"/>
@@ -9750,19 +9750,19 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>1206</v>
+        <v>1213</v>
       </c>
       <c r="B365" t="n">
         <v>2</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
@@ -9775,19 +9775,19 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>1207</v>
+        <v>1216</v>
       </c>
       <c r="B366" t="n">
         <v>2</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
+          <t>Tian Sheng You 19</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
           <t>Yuan Xiang You 16</t>
-        </is>
-      </c>
-      <c r="D366" t="inlineStr">
-        <is>
-          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
@@ -9800,19 +9800,19 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="B367" t="n">
         <v>2</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
+          <t>Yuan Xiang You 16</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
           <t>Tian Sheng You 19</t>
-        </is>
-      </c>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E367" t="inlineStr"/>
@@ -9825,19 +9825,19 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>1216</v>
+        <v>1220</v>
       </c>
       <c r="B368" t="n">
         <v>2</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
+          <t>Hua Guang 68</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Run Ji 17</t>
         </is>
       </c>
       <c r="E368" t="inlineStr"/>
@@ -9850,19 +9850,19 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="B369" t="n">
         <v>2</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Run Ji 17</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
+          <t>Run Ji 15</t>
         </is>
       </c>
       <c r="E369" t="inlineStr"/>
@@ -9875,19 +9875,19 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>1220</v>
+        <v>1225</v>
       </c>
       <c r="B370" t="n">
         <v>2</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Hua Guang 68</t>
+          <t>Hai Xiang 17</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Run Ji 17</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E370" t="inlineStr"/>
@@ -9900,19 +9900,19 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>1222</v>
+        <v>1226</v>
       </c>
       <c r="B371" t="n">
         <v>2</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Run Ji 17</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Run Ji 15</t>
+          <t>Rui Yun 21</t>
         </is>
       </c>
       <c r="E371" t="inlineStr"/>
@@ -9925,19 +9925,19 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="B372" t="n">
         <v>2</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Hai Xiang 17</t>
+          <t>Hongheng189</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Hong Da Hai 88</t>
         </is>
       </c>
       <c r="E372" t="inlineStr"/>
@@ -9950,19 +9950,19 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="B373" t="n">
         <v>2</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
+          <t>Tian Sheng You 19</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
           <t>Yuan Xiang You 16</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>Rui Yun 21</t>
         </is>
       </c>
       <c r="E373" t="inlineStr"/>
@@ -9975,19 +9975,19 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="B374" t="n">
         <v>2</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Hongheng189</t>
+          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Hong Da Hai 88</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E374" t="inlineStr"/>
@@ -10000,14 +10000,14 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>1229</v>
+        <v>1235</v>
       </c>
       <c r="B375" t="n">
         <v>2</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
+          <t>Yicheng27</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -10025,19 +10025,19 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>1230</v>
+        <v>1237</v>
       </c>
       <c r="B376" t="n">
         <v>2</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Xin Sheng 17</t>
         </is>
       </c>
       <c r="E376" t="inlineStr"/>
@@ -10050,19 +10050,19 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>1235</v>
+        <v>1241</v>
       </c>
       <c r="B377" t="n">
         <v>2</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Yicheng27</t>
+          <t>Hongheng169</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
@@ -10075,19 +10075,19 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>1237</v>
+        <v>1243</v>
       </c>
       <c r="B378" t="n">
         <v>2</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Xin Sheng 17</t>
+          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="E378" t="inlineStr"/>
@@ -10100,19 +10100,19 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>1241</v>
+        <v>1251</v>
       </c>
       <c r="B379" t="n">
         <v>2</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="E379" t="inlineStr"/>
@@ -10125,19 +10125,19 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>1243</v>
+        <v>1252</v>
       </c>
       <c r="B380" t="n">
         <v>2</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Hongheng169</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
+          <t>Shun Kai 7</t>
         </is>
       </c>
       <c r="E380" t="inlineStr"/>
@@ -10150,7 +10150,7 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>1251</v>
+        <v>1254</v>
       </c>
       <c r="B381" t="n">
         <v>2</v>
@@ -10162,7 +10162,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
+          <t>Qi Chen 6</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
@@ -10175,19 +10175,19 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="B382" t="n">
         <v>2</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Shun Kai 7</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
@@ -10200,19 +10200,19 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="B383" t="n">
         <v>2</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
+          <t>Heng Xing 9</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
           <t>Yuan Xiang You 16</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>Qi Chen 6</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
@@ -10225,7 +10225,7 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="B384" t="n">
         <v>2</v>
@@ -10250,7 +10250,7 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="B385" t="n">
         <v>2</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Xin Sheng 17</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
@@ -10275,19 +10275,19 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>1258</v>
+        <v>1263</v>
       </c>
       <c r="B386" t="n">
         <v>2</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Xin Ke 16</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Hui Chen 118</t>
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
@@ -10300,19 +10300,19 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="B387" t="n">
         <v>2</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
+          <t>Yuan Xiang You 16</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
           <t>Heng Xing 9</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>Xin Sheng 17</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
@@ -10325,19 +10325,19 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>1263</v>
+        <v>1268</v>
       </c>
       <c r="B388" t="n">
         <v>2</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Xin Ke 16</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Hui Chen 118</t>
+          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
@@ -10350,19 +10350,19 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>1265</v>
+        <v>1271</v>
       </c>
       <c r="B389" t="n">
         <v>2</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Xin Ke 16</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Hui Chen 118</t>
         </is>
       </c>
       <c r="E389" t="inlineStr"/>
@@ -10375,19 +10375,19 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>1268</v>
+        <v>1282</v>
       </c>
       <c r="B390" t="n">
         <v>2</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
+          <t>Hongheng169</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
           <t>Yuan Xiang You 16</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="E390" t="inlineStr"/>
@@ -10400,19 +10400,19 @@
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>1271</v>
+        <v>1283</v>
       </c>
       <c r="B391" t="n">
         <v>2</v>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Xin Ke 16</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Hui Chen 118</t>
+          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="E391" t="inlineStr"/>
@@ -10425,7 +10425,7 @@
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>1282</v>
+        <v>1286</v>
       </c>
       <c r="B392" t="n">
         <v>2</v>
@@ -10450,19 +10450,19 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>1283</v>
+        <v>1288</v>
       </c>
       <c r="B393" t="n">
         <v>2</v>
       </c>
       <c r="C393" t="inlineStr">
         <is>
+          <t>Tian Sheng You 19</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
           <t>Yuan Xiang You 16</t>
-        </is>
-      </c>
-      <c r="D393" t="inlineStr">
-        <is>
-          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="E393" t="inlineStr"/>
@@ -10475,14 +10475,14 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="B394" t="n">
         <v>2</v>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Qi Chen 6</t>
+          <t>Xin Run 20</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -10500,19 +10500,19 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>1286</v>
+        <v>1298</v>
       </c>
       <c r="B395" t="n">
         <v>2</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Hai Hang You 7</t>
         </is>
       </c>
       <c r="E395" t="inlineStr"/>
@@ -10525,19 +10525,19 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>1288</v>
+        <v>1300</v>
       </c>
       <c r="B396" t="n">
         <v>2</v>
       </c>
       <c r="C396" t="inlineStr">
         <is>
+          <t>Yuan Xiang You 16</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
           <t>Tian Sheng You 19</t>
-        </is>
-      </c>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>Yuan Xiang You 16</t>
         </is>
       </c>
       <c r="E396" t="inlineStr"/>
@@ -10550,14 +10550,14 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>1290</v>
+        <v>1301</v>
       </c>
       <c r="B397" t="n">
         <v>2</v>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Xin Run 20</t>
+          <t>Yicheng27</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -10575,7 +10575,7 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>1298</v>
+        <v>1303</v>
       </c>
       <c r="B398" t="n">
         <v>2</v>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Hai Hang You 7</t>
+          <t>Hongheng189</t>
         </is>
       </c>
       <c r="E398" t="inlineStr"/>
@@ -10600,19 +10600,19 @@
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>1300</v>
+        <v>1307</v>
       </c>
       <c r="B399" t="n">
         <v>2</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Hui Chen 118</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
+          <t>Jin Shi 77</t>
         </is>
       </c>
       <c r="E399" t="inlineStr"/>
@@ -10625,19 +10625,19 @@
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>1301</v>
+        <v>1308</v>
       </c>
       <c r="B400" t="n">
         <v>2</v>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Yicheng27</t>
+          <t>Chaoyang301</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Chao Yang 302</t>
         </is>
       </c>
       <c r="E400" t="inlineStr"/>
@@ -10650,22 +10650,26 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>1303</v>
+        <v>1309</v>
       </c>
       <c r="B401" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Yuan Xiang You 16</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Hongheng189</t>
-        </is>
-      </c>
-      <c r="E401" t="inlineStr"/>
+          <t>Heng Xing 9</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Dong Gang You66</t>
+        </is>
+      </c>
       <c r="F401" t="inlineStr"/>
       <c r="G401" t="inlineStr"/>
       <c r="H401" t="inlineStr"/>
@@ -10675,19 +10679,19 @@
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>1307</v>
+        <v>1312</v>
       </c>
       <c r="B402" t="n">
         <v>2</v>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Hui Chen 118</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Jin Shi 77</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="E402" t="inlineStr"/>
@@ -10700,19 +10704,19 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>1308</v>
+        <v>1322</v>
       </c>
       <c r="B403" t="n">
         <v>2</v>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Chaoyang301</t>
+          <t>Dong Sheng You 77</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Chao Yang 302</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="E403" t="inlineStr"/>
@@ -10725,26 +10729,22 @@
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>1309</v>
+        <v>1336</v>
       </c>
       <c r="B404" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Yicheng27</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
-        </is>
-      </c>
-      <c r="E404" t="inlineStr">
-        <is>
           <t>Dong Gang You66</t>
         </is>
       </c>
+      <c r="E404" t="inlineStr"/>
       <c r="F404" t="inlineStr"/>
       <c r="G404" t="inlineStr"/>
       <c r="H404" t="inlineStr"/>
@@ -10754,19 +10754,19 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>1312</v>
+        <v>1337</v>
       </c>
       <c r="B405" t="n">
         <v>2</v>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Hua Ran 177</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="E405" t="inlineStr"/>
@@ -10779,22 +10779,26 @@
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>1322</v>
+        <v>1339</v>
       </c>
       <c r="B406" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Dong Sheng You 77</t>
+          <t>Run Ji 17</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
-        </is>
-      </c>
-      <c r="E406" t="inlineStr"/>
+          <t>Yong Cheng 97</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Yong Cheng 97</t>
+        </is>
+      </c>
       <c r="F406" t="inlineStr"/>
       <c r="G406" t="inlineStr"/>
       <c r="H406" t="inlineStr"/>
@@ -10804,14 +10808,14 @@
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>1336</v>
+        <v>1349</v>
       </c>
       <c r="B407" t="n">
         <v>2</v>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Yicheng27</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -10829,22 +10833,26 @@
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>1337</v>
+        <v>1352</v>
       </c>
       <c r="B408" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Hua Ran 177</t>
+          <t>Xin Sheng 17</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
-        </is>
-      </c>
-      <c r="E408" t="inlineStr"/>
+          <t>Xin Sheng 17</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Dong Gang You66</t>
+        </is>
+      </c>
       <c r="F408" t="inlineStr"/>
       <c r="G408" t="inlineStr"/>
       <c r="H408" t="inlineStr"/>
@@ -10854,26 +10862,22 @@
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>1339</v>
+        <v>1353</v>
       </c>
       <c r="B409" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Run Ji 17</t>
+          <t>Yicheng27</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Yong Cheng 97</t>
-        </is>
-      </c>
-      <c r="E409" t="inlineStr">
-        <is>
-          <t>Yong Cheng 97</t>
-        </is>
-      </c>
+          <t>Dong Gang You66</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr"/>
       <c r="F409" t="inlineStr"/>
       <c r="G409" t="inlineStr"/>
       <c r="H409" t="inlineStr"/>
@@ -10883,19 +10887,19 @@
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>1349</v>
+        <v>1356</v>
       </c>
       <c r="B410" t="n">
         <v>2</v>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Yuanxiangyou16</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Tian Sheng You 19</t>
         </is>
       </c>
       <c r="E410" t="inlineStr"/>
@@ -10908,26 +10912,22 @@
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>1352</v>
+        <v>1362</v>
       </c>
       <c r="B411" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Xin Sheng 17</t>
+          <t>Ning Feng You 1</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Xin Sheng 17</t>
-        </is>
-      </c>
-      <c r="E411" t="inlineStr">
-        <is>
           <t>Dong Gang You66</t>
         </is>
       </c>
+      <c r="E411" t="inlineStr"/>
       <c r="F411" t="inlineStr"/>
       <c r="G411" t="inlineStr"/>
       <c r="H411" t="inlineStr"/>
@@ -10937,7 +10937,7 @@
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>1353</v>
+        <v>1363</v>
       </c>
       <c r="B412" t="n">
         <v>2</v>
@@ -10962,22 +10962,26 @@
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>1356</v>
+        <v>1366</v>
       </c>
       <c r="B413" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Yuanxiangyou16</t>
+          <t>Long Yu 18</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Tian Sheng You 19</t>
-        </is>
-      </c>
-      <c r="E413" t="inlineStr"/>
+          <t>Yiding6</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Yiding6</t>
+        </is>
+      </c>
       <c r="F413" t="inlineStr"/>
       <c r="G413" t="inlineStr"/>
       <c r="H413" t="inlineStr"/>
@@ -10987,14 +10991,14 @@
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>1362</v>
+        <v>1368</v>
       </c>
       <c r="B414" t="n">
         <v>2</v>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Ning Feng You 1</t>
+          <t>Yicheng27</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -11012,19 +11016,19 @@
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>1363</v>
+        <v>1369</v>
       </c>
       <c r="B415" t="n">
         <v>2</v>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Yicheng27</t>
+          <t>Hongheng169</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Zhoushun5</t>
         </is>
       </c>
       <c r="E415" t="inlineStr"/>
@@ -11037,26 +11041,22 @@
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>1366</v>
+        <v>1370</v>
       </c>
       <c r="B416" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Long Yu 18</t>
+          <t>Hong Da Hai 88</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Yiding6</t>
-        </is>
-      </c>
-      <c r="E416" t="inlineStr">
-        <is>
-          <t>Yiding6</t>
-        </is>
-      </c>
+          <t>Dong Gang You66</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr"/>
       <c r="F416" t="inlineStr"/>
       <c r="G416" t="inlineStr"/>
       <c r="H416" t="inlineStr"/>
@@ -11066,7 +11066,7 @@
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>1368</v>
+        <v>1371</v>
       </c>
       <c r="B417" t="n">
         <v>2</v>
@@ -11091,19 +11091,19 @@
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>1369</v>
+        <v>1375</v>
       </c>
       <c r="B418" t="n">
         <v>2</v>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Shun Ping 17</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Zhoushun5</t>
+          <t>Xin Sheng 17</t>
         </is>
       </c>
       <c r="E418" t="inlineStr"/>
@@ -11116,19 +11116,19 @@
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>1370</v>
+        <v>1377</v>
       </c>
       <c r="B419" t="n">
         <v>2</v>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Hong Da Hai 88</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Yong Cheng 166</t>
         </is>
       </c>
       <c r="E419" t="inlineStr"/>
@@ -11141,19 +11141,19 @@
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>1371</v>
+        <v>1378</v>
       </c>
       <c r="B420" t="n">
         <v>2</v>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Yicheng27</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Huaran166</t>
         </is>
       </c>
       <c r="E420" t="inlineStr"/>
@@ -11166,19 +11166,19 @@
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>1375</v>
+        <v>1395</v>
       </c>
       <c r="B421" t="n">
         <v>2</v>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Shun Ping 17</t>
+          <t>Hai Xiang 5</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Xin Sheng 17</t>
+          <t>Hai Xiang 5</t>
         </is>
       </c>
       <c r="E421" t="inlineStr"/>
@@ -11191,19 +11191,19 @@
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>1377</v>
+        <v>1399</v>
       </c>
       <c r="B422" t="n">
         <v>2</v>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Fu Jie 168</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Yong Cheng 166</t>
+          <t>Ning Feng Xing Chen</t>
         </is>
       </c>
       <c r="E422" t="inlineStr"/>
@@ -11216,19 +11216,19 @@
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>1378</v>
+        <v>1401</v>
       </c>
       <c r="B423" t="n">
         <v>2</v>
       </c>
       <c r="C423" t="inlineStr">
         <is>
+          <t>Heng Xing 9</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
           <t>Dong Gang You66</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>Huaran166</t>
         </is>
       </c>
       <c r="E423" t="inlineStr"/>
@@ -11241,44 +11241,60 @@
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>1395</v>
+        <v>1406</v>
       </c>
       <c r="B424" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Hai Xiang 5</t>
+          <t>Xin Shi Ji 7</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Hai Xiang 5</t>
-        </is>
-      </c>
-      <c r="E424" t="inlineStr"/>
-      <c r="F424" t="inlineStr"/>
-      <c r="G424" t="inlineStr"/>
-      <c r="H424" t="inlineStr"/>
+          <t>Zhong Fan 323</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Zhongdayou288</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Zhong Fan 323</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>Zhongdayou288</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>Zhong Fan 323</t>
+        </is>
+      </c>
       <c r="I424" t="inlineStr"/>
       <c r="J424" t="inlineStr"/>
       <c r="K424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>1399</v>
+        <v>1408</v>
       </c>
       <c r="B425" t="n">
         <v>2</v>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Fu Jie 168</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Ning Feng Xing Chen</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="E425" t="inlineStr"/>
@@ -11291,19 +11307,19 @@
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>1401</v>
+        <v>1412</v>
       </c>
       <c r="B426" t="n">
         <v>2</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Chao Yang302</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Chao Yang302</t>
         </is>
       </c>
       <c r="E426" t="inlineStr"/>
@@ -11316,48 +11332,36 @@
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>1406</v>
+        <v>1420</v>
       </c>
       <c r="B427" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Xin Shi Ji 7</t>
+          <t>Dong Sheng You 77</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Zhong Fan 323</t>
+          <t>Shun Ping 19</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Zhongdayou288</t>
-        </is>
-      </c>
-      <c r="F427" t="inlineStr">
-        <is>
-          <t>Zhong Fan 323</t>
-        </is>
-      </c>
-      <c r="G427" t="inlineStr">
-        <is>
-          <t>Zhongdayou288</t>
-        </is>
-      </c>
-      <c r="H427" t="inlineStr">
-        <is>
-          <t>Zhong Fan 323</t>
-        </is>
-      </c>
+          <t>Shun Ping 19</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr"/>
+      <c r="G427" t="inlineStr"/>
+      <c r="H427" t="inlineStr"/>
       <c r="I427" t="inlineStr"/>
       <c r="J427" t="inlineStr"/>
       <c r="K427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>1408</v>
+        <v>1422</v>
       </c>
       <c r="B428" t="n">
         <v>2</v>
@@ -11382,19 +11386,19 @@
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>1412</v>
+        <v>1430</v>
       </c>
       <c r="B429" t="n">
         <v>2</v>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Chao Yang302</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Chao Yang302</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="E429" t="inlineStr"/>
@@ -11407,26 +11411,22 @@
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>1420</v>
+        <v>1434</v>
       </c>
       <c r="B430" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Dong Sheng You 77</t>
+          <t>Si Jie 21</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Shun Ping 19</t>
-        </is>
-      </c>
-      <c r="E430" t="inlineStr">
-        <is>
-          <t>Shun Ping 19</t>
-        </is>
-      </c>
+          <t>Si Jie 21</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr"/>
       <c r="F430" t="inlineStr"/>
       <c r="G430" t="inlineStr"/>
       <c r="H430" t="inlineStr"/>
@@ -11436,44 +11436,72 @@
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>1422</v>
+        <v>1439</v>
       </c>
       <c r="B431" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Bai Da 28</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
-        </is>
-      </c>
-      <c r="E431" t="inlineStr"/>
-      <c r="F431" t="inlineStr"/>
-      <c r="G431" t="inlineStr"/>
-      <c r="H431" t="inlineStr"/>
-      <c r="I431" t="inlineStr"/>
-      <c r="J431" t="inlineStr"/>
-      <c r="K431" t="inlineStr"/>
+          <t>Hai Hang You 7</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Jin Shi 77</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Bai Da 28</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>Hai Hang You 7</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>Jin Shi 77</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>Zhou Hai Qing 1</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>Zhouhaiqing16</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Zhouhaiqing16</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>1430</v>
+        <v>1443</v>
       </c>
       <c r="B432" t="n">
         <v>2</v>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Jin Hui 17</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Jin Hui 17</t>
         </is>
       </c>
       <c r="E432" t="inlineStr"/>
@@ -11486,19 +11514,19 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>1434</v>
+        <v>1452</v>
       </c>
       <c r="B433" t="n">
         <v>2</v>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Si Jie 21</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Si Jie 21</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="E433" t="inlineStr"/>
@@ -11511,72 +11539,48 @@
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>1439</v>
+        <v>1454</v>
       </c>
       <c r="B434" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Bai Da 28</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Hai Hang You 7</t>
+          <t>Xin Kai 1</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Jin Shi 77</t>
-        </is>
-      </c>
-      <c r="F434" t="inlineStr">
-        <is>
-          <t>Bai Da 28</t>
-        </is>
-      </c>
-      <c r="G434" t="inlineStr">
-        <is>
-          <t>Hai Hang You 7</t>
-        </is>
-      </c>
-      <c r="H434" t="inlineStr">
-        <is>
-          <t>Jin Shi 77</t>
-        </is>
-      </c>
-      <c r="I434" t="inlineStr">
-        <is>
-          <t>Zhou Hai Qing 1</t>
-        </is>
-      </c>
-      <c r="J434" t="inlineStr">
-        <is>
-          <t>Zhouhaiqing16</t>
-        </is>
-      </c>
-      <c r="K434" t="inlineStr">
-        <is>
-          <t>Zhouhaiqing16</t>
-        </is>
-      </c>
+          <t>Dong Gang You66</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" t="inlineStr"/>
+      <c r="H434" t="inlineStr"/>
+      <c r="I434" t="inlineStr"/>
+      <c r="J434" t="inlineStr"/>
+      <c r="K434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>1443</v>
+        <v>1455</v>
       </c>
       <c r="B435" t="n">
         <v>2</v>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Jin Hui 17</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Jin Hui 17</t>
+          <t>Dong Sheng You 77</t>
         </is>
       </c>
       <c r="E435" t="inlineStr"/>
@@ -11589,19 +11593,19 @@
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>1452</v>
+        <v>1462</v>
       </c>
       <c r="B436" t="n">
         <v>2</v>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Hongheng169</t>
         </is>
       </c>
       <c r="E436" t="inlineStr"/>
@@ -11614,26 +11618,22 @@
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>1454</v>
+        <v>1467</v>
       </c>
       <c r="B437" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C437" t="inlineStr">
         <is>
+          <t>Heng Xing 9</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
           <t>Dong Gang You66</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>Xin Kai 1</t>
-        </is>
-      </c>
-      <c r="E437" t="inlineStr">
-        <is>
-          <t>Dong Gang You66</t>
-        </is>
-      </c>
+      <c r="E437" t="inlineStr"/>
       <c r="F437" t="inlineStr"/>
       <c r="G437" t="inlineStr"/>
       <c r="H437" t="inlineStr"/>
@@ -11643,19 +11643,19 @@
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>1455</v>
+        <v>1475</v>
       </c>
       <c r="B438" t="n">
         <v>2</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Hui Chen 118</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Dong Sheng You 77</t>
+          <t>Jin Hui 17</t>
         </is>
       </c>
       <c r="E438" t="inlineStr"/>
@@ -11668,19 +11668,19 @@
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>1462</v>
+        <v>1476</v>
       </c>
       <c r="B439" t="n">
         <v>2</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Shun Ping 17</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Kang--Fa--125</t>
         </is>
       </c>
       <c r="E439" t="inlineStr"/>
@@ -11693,22 +11693,26 @@
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>1467</v>
+        <v>1479</v>
       </c>
       <c r="B440" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
-        </is>
-      </c>
-      <c r="E440" t="inlineStr"/>
+          <t>Hua Ran 177</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Hongheng169</t>
+        </is>
+      </c>
       <c r="F440" t="inlineStr"/>
       <c r="G440" t="inlineStr"/>
       <c r="H440" t="inlineStr"/>
@@ -11718,19 +11722,19 @@
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>1472</v>
+        <v>1481</v>
       </c>
       <c r="B441" t="n">
         <v>2</v>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Chaoyang301</t>
+          <t>Hai Xiang 5</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Fu Jie 168</t>
+          <t>Hui Chen 118</t>
         </is>
       </c>
       <c r="E441" t="inlineStr"/>
@@ -11743,19 +11747,19 @@
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>1473</v>
+        <v>1482</v>
       </c>
       <c r="B442" t="n">
         <v>2</v>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Xin Ke 16</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>An Tong 27</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="E442" t="inlineStr"/>
@@ -11768,19 +11772,19 @@
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>1475</v>
+        <v>1486</v>
       </c>
       <c r="B443" t="n">
         <v>2</v>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Hui Chen 118</t>
+          <t>Hongheng169</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Jin Hui 17</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="E443" t="inlineStr"/>
@@ -11793,19 +11797,19 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>1476</v>
+        <v>1491</v>
       </c>
       <c r="B444" t="n">
         <v>2</v>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Shun Ping 17</t>
+          <t>Zhong Fan 323</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Kang--Fa--125</t>
+          <t>Jin Se Hai Yang 20</t>
         </is>
       </c>
       <c r="E444" t="inlineStr"/>
@@ -11818,26 +11822,22 @@
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>1479</v>
+        <v>1495</v>
       </c>
       <c r="B445" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C445" t="inlineStr">
         <is>
+          <t>Heng Xing 9</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
           <t>Dong Gang You66</t>
         </is>
       </c>
-      <c r="D445" t="inlineStr">
-        <is>
-          <t>Hua Ran 177</t>
-        </is>
-      </c>
-      <c r="E445" t="inlineStr">
-        <is>
-          <t>Hongheng169</t>
-        </is>
-      </c>
+      <c r="E445" t="inlineStr"/>
       <c r="F445" t="inlineStr"/>
       <c r="G445" t="inlineStr"/>
       <c r="H445" t="inlineStr"/>
@@ -11847,19 +11847,19 @@
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>1481</v>
+        <v>1499</v>
       </c>
       <c r="B446" t="n">
         <v>2</v>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Hai Xiang 5</t>
+          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Hui Chen 118</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="E446" t="inlineStr"/>
@@ -11872,14 +11872,14 @@
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>1482</v>
+        <v>1504</v>
       </c>
       <c r="B447" t="n">
         <v>2</v>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Xin Ke 16</t>
+          <t>Hongheng169</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -11897,14 +11897,14 @@
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>1486</v>
+        <v>1513</v>
       </c>
       <c r="B448" t="n">
         <v>2</v>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -11922,19 +11922,19 @@
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>1491</v>
+        <v>1516</v>
       </c>
       <c r="B449" t="n">
         <v>2</v>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Zhong Fan 323</t>
+          <t>Zhou Da You 7</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Jin Se Hai Yang 20</t>
+          <t>Hai Xiang 17</t>
         </is>
       </c>
       <c r="E449" t="inlineStr"/>
@@ -11947,19 +11947,19 @@
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>1495</v>
+        <v>1517</v>
       </c>
       <c r="B450" t="n">
         <v>2</v>
       </c>
       <c r="C450" t="inlineStr">
         <is>
+          <t>Zhong Xing You 6</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
           <t>Heng Xing 9</t>
-        </is>
-      </c>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>Dong Gang You66</t>
         </is>
       </c>
       <c r="E450" t="inlineStr"/>
@@ -11972,19 +11972,19 @@
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>1499</v>
+        <v>1521</v>
       </c>
       <c r="B451" t="n">
         <v>2</v>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Yicheng27</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Le Yang 1</t>
         </is>
       </c>
       <c r="E451" t="inlineStr"/>
@@ -11997,19 +11997,19 @@
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>1503</v>
+        <v>1527</v>
       </c>
       <c r="B452" t="n">
         <v>2</v>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Zhou Shun 10</t>
+          <t>Le Yang 1</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Yicheng27</t>
         </is>
       </c>
       <c r="E452" t="inlineStr"/>
@@ -12022,19 +12022,19 @@
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>1504</v>
+        <v>1530</v>
       </c>
       <c r="B453" t="n">
         <v>2</v>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Le Yang 1</t>
         </is>
       </c>
       <c r="E453" t="inlineStr"/>
@@ -12047,19 +12047,19 @@
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>1513</v>
+        <v>1531</v>
       </c>
       <c r="B454" t="n">
         <v>2</v>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Le Yang 1</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Dong Gang You66</t>
+          <t>Yicheng27</t>
         </is>
       </c>
       <c r="E454" t="inlineStr"/>
@@ -12072,19 +12072,19 @@
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>1516</v>
+        <v>1536</v>
       </c>
       <c r="B455" t="n">
         <v>2</v>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Zhou Da You 7</t>
+          <t>Zhe Hai You 5</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Hai Xiang 17</t>
+          <t>Run Ze 11</t>
         </is>
       </c>
       <c r="E455" t="inlineStr"/>
@@ -12097,19 +12097,19 @@
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>1517</v>
+        <v>1539</v>
       </c>
       <c r="B456" t="n">
         <v>2</v>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Zhong Xing You 6</t>
+          <t>Chaoyang301</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Le Yang 1</t>
         </is>
       </c>
       <c r="E456" t="inlineStr"/>
@@ -12122,14 +12122,14 @@
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>1521</v>
+        <v>1543</v>
       </c>
       <c r="B457" t="n">
         <v>2</v>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Yicheng27</t>
+          <t>Xin Kai 1</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -12147,19 +12147,19 @@
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>1527</v>
+        <v>1550</v>
       </c>
       <c r="B458" t="n">
         <v>2</v>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Le Yang 1</t>
+          <t>Shen Jia 9</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Yicheng27</t>
+          <t>Jin Hui 17</t>
         </is>
       </c>
       <c r="E458" t="inlineStr"/>
@@ -12172,19 +12172,19 @@
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>1530</v>
+        <v>1553</v>
       </c>
       <c r="B459" t="n">
         <v>2</v>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Bo Hai Gong 7</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Le Yang 1</t>
+          <t>Bo Hai Gong 7</t>
         </is>
       </c>
       <c r="E459" t="inlineStr"/>
@@ -12197,19 +12197,19 @@
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>1531</v>
+        <v>1556</v>
       </c>
       <c r="B460" t="n">
         <v>2</v>
       </c>
       <c r="C460" t="inlineStr">
         <is>
+          <t>Heng Xing 9</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
           <t>Le Yang 1</t>
-        </is>
-      </c>
-      <c r="D460" t="inlineStr">
-        <is>
-          <t>Yicheng27</t>
         </is>
       </c>
       <c r="E460" t="inlineStr"/>
@@ -12222,19 +12222,19 @@
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>1536</v>
+        <v>1558</v>
       </c>
       <c r="B461" t="n">
         <v>2</v>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Zhe Hai You 5</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Run Ze 11</t>
+          <t>Le Yang 1</t>
         </is>
       </c>
       <c r="E461" t="inlineStr"/>
@@ -12247,14 +12247,14 @@
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>1539</v>
+        <v>1559</v>
       </c>
       <c r="B462" t="n">
         <v>2</v>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Chaoyang301</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -12272,14 +12272,14 @@
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>1543</v>
+        <v>1565</v>
       </c>
       <c r="B463" t="n">
         <v>2</v>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Xin Kai 1</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -12297,19 +12297,19 @@
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>1550</v>
+        <v>1572</v>
       </c>
       <c r="B464" t="n">
         <v>2</v>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Shen Jia 9</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Jin Hui 17</t>
+          <t>Yi Shun 11</t>
         </is>
       </c>
       <c r="E464" t="inlineStr"/>
@@ -12322,19 +12322,19 @@
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>1553</v>
+        <v>1573</v>
       </c>
       <c r="B465" t="n">
         <v>2</v>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Bo Hai Gong 7</t>
+          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>Bo Hai Gong 7</t>
+          <t>Le Yang 1</t>
         </is>
       </c>
       <c r="E465" t="inlineStr"/>
@@ -12347,19 +12347,19 @@
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>1556</v>
+        <v>1576</v>
       </c>
       <c r="B466" t="n">
         <v>2</v>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Yicheng27</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Le Yang 1</t>
+          <t>Yi Shun 11</t>
         </is>
       </c>
       <c r="E466" t="inlineStr"/>
@@ -12372,7 +12372,7 @@
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>1558</v>
+        <v>1577</v>
       </c>
       <c r="B467" t="n">
         <v>2</v>
@@ -12397,19 +12397,19 @@
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>1559</v>
+        <v>1585</v>
       </c>
       <c r="B468" t="n">
         <v>2</v>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Ming Feng 7</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Le Yang 1</t>
+          <t>Ming Feng 7</t>
         </is>
       </c>
       <c r="E468" t="inlineStr"/>
@@ -12422,14 +12422,14 @@
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>1565</v>
+        <v>1594</v>
       </c>
       <c r="B469" t="n">
         <v>2</v>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Hai Zhi Run 69</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -12447,19 +12447,19 @@
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>1572</v>
+        <v>1597</v>
       </c>
       <c r="B470" t="n">
         <v>2</v>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Hongheng189</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Yi Shun 11</t>
+          <t>Le Yang 1</t>
         </is>
       </c>
       <c r="E470" t="inlineStr"/>
@@ -12472,14 +12472,14 @@
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>1573</v>
+        <v>1603</v>
       </c>
       <c r="B471" t="n">
         <v>2</v>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Hongheng169</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -12497,19 +12497,19 @@
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>1576</v>
+        <v>1605</v>
       </c>
       <c r="B472" t="n">
         <v>2</v>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Yicheng27</t>
+          <t>Hongheng169</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Yi Shun 11</t>
+          <t>Le Yang 1</t>
         </is>
       </c>
       <c r="E472" t="inlineStr"/>
@@ -12522,19 +12522,19 @@
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>1577</v>
+        <v>1617</v>
       </c>
       <c r="B473" t="n">
         <v>2</v>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Heng Xing 9</t>
+          <t>Run Ji 17</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Le Yang 1</t>
+          <t>Yong Cheng 97</t>
         </is>
       </c>
       <c r="E473" t="inlineStr"/>
@@ -12547,19 +12547,19 @@
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>1585</v>
+        <v>1618</v>
       </c>
       <c r="B474" t="n">
         <v>2</v>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Ming Feng 7</t>
+          <t>Le Yang 1</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Ming Feng 7</t>
+          <t>Le Yang 1</t>
         </is>
       </c>
       <c r="E474" t="inlineStr"/>
@@ -12572,14 +12572,14 @@
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>1594</v>
+        <v>1621</v>
       </c>
       <c r="B475" t="n">
         <v>2</v>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Hai Zhi Run 69</t>
+          <t>Hongheng169</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -12597,14 +12597,14 @@
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>1597</v>
+        <v>1622</v>
       </c>
       <c r="B476" t="n">
         <v>2</v>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Hongheng189</t>
+          <t>Le Yang 1</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -12622,19 +12622,19 @@
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>1603</v>
+        <v>1623</v>
       </c>
       <c r="B477" t="n">
         <v>2</v>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Run Ji 17</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Le Yang 1</t>
+          <t>Hua Guang 68</t>
         </is>
       </c>
       <c r="E477" t="inlineStr"/>
@@ -12647,19 +12647,19 @@
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>1605</v>
+        <v>1627</v>
       </c>
       <c r="B478" t="n">
         <v>2</v>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Hua Guang 68</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Le Yang 1</t>
+          <t>Run Ji 17</t>
         </is>
       </c>
       <c r="E478" t="inlineStr"/>
@@ -12672,19 +12672,19 @@
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>1617</v>
+        <v>1632</v>
       </c>
       <c r="B479" t="n">
         <v>2</v>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Run Ji 17</t>
+          <t>Fu Jie 168</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Yong Cheng 97</t>
+          <t>Chao Yang 302</t>
         </is>
       </c>
       <c r="E479" t="inlineStr"/>
@@ -12697,19 +12697,19 @@
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>1618</v>
+        <v>1636</v>
       </c>
       <c r="B480" t="n">
         <v>2</v>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Le Yang 1</t>
+          <t>Hai Hang You 7</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Le Yang 1</t>
+          <t>Zhongdayou288</t>
         </is>
       </c>
       <c r="E480" t="inlineStr"/>
@@ -12722,22 +12722,26 @@
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>1621</v>
+        <v>1637</v>
       </c>
       <c r="B481" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Hongheng169</t>
+          <t>Zhongdayou288</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Le Yang 1</t>
-        </is>
-      </c>
-      <c r="E481" t="inlineStr"/>
+          <t>Jin Shi 77</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>Fu Jie 168</t>
+        </is>
+      </c>
       <c r="F481" t="inlineStr"/>
       <c r="G481" t="inlineStr"/>
       <c r="H481" t="inlineStr"/>
@@ -12745,160 +12749,6 @@
       <c r="J481" t="inlineStr"/>
       <c r="K481" t="inlineStr"/>
     </row>
-    <row r="482">
-      <c r="A482" t="n">
-        <v>1622</v>
-      </c>
-      <c r="B482" t="n">
-        <v>2</v>
-      </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>Le Yang 1</t>
-        </is>
-      </c>
-      <c r="D482" t="inlineStr">
-        <is>
-          <t>Le Yang 1</t>
-        </is>
-      </c>
-      <c r="E482" t="inlineStr"/>
-      <c r="F482" t="inlineStr"/>
-      <c r="G482" t="inlineStr"/>
-      <c r="H482" t="inlineStr"/>
-      <c r="I482" t="inlineStr"/>
-      <c r="J482" t="inlineStr"/>
-      <c r="K482" t="inlineStr"/>
-    </row>
-    <row r="483">
-      <c r="A483" t="n">
-        <v>1623</v>
-      </c>
-      <c r="B483" t="n">
-        <v>2</v>
-      </c>
-      <c r="C483" t="inlineStr">
-        <is>
-          <t>Run Ji 17</t>
-        </is>
-      </c>
-      <c r="D483" t="inlineStr">
-        <is>
-          <t>Hua Guang 68</t>
-        </is>
-      </c>
-      <c r="E483" t="inlineStr"/>
-      <c r="F483" t="inlineStr"/>
-      <c r="G483" t="inlineStr"/>
-      <c r="H483" t="inlineStr"/>
-      <c r="I483" t="inlineStr"/>
-      <c r="J483" t="inlineStr"/>
-      <c r="K483" t="inlineStr"/>
-    </row>
-    <row r="484">
-      <c r="A484" t="n">
-        <v>1627</v>
-      </c>
-      <c r="B484" t="n">
-        <v>2</v>
-      </c>
-      <c r="C484" t="inlineStr">
-        <is>
-          <t>Hua Guang 68</t>
-        </is>
-      </c>
-      <c r="D484" t="inlineStr">
-        <is>
-          <t>Run Ji 17</t>
-        </is>
-      </c>
-      <c r="E484" t="inlineStr"/>
-      <c r="F484" t="inlineStr"/>
-      <c r="G484" t="inlineStr"/>
-      <c r="H484" t="inlineStr"/>
-      <c r="I484" t="inlineStr"/>
-      <c r="J484" t="inlineStr"/>
-      <c r="K484" t="inlineStr"/>
-    </row>
-    <row r="485">
-      <c r="A485" t="n">
-        <v>1632</v>
-      </c>
-      <c r="B485" t="n">
-        <v>2</v>
-      </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>Fu Jie 168</t>
-        </is>
-      </c>
-      <c r="D485" t="inlineStr">
-        <is>
-          <t>Chao Yang 302</t>
-        </is>
-      </c>
-      <c r="E485" t="inlineStr"/>
-      <c r="F485" t="inlineStr"/>
-      <c r="G485" t="inlineStr"/>
-      <c r="H485" t="inlineStr"/>
-      <c r="I485" t="inlineStr"/>
-      <c r="J485" t="inlineStr"/>
-      <c r="K485" t="inlineStr"/>
-    </row>
-    <row r="486">
-      <c r="A486" t="n">
-        <v>1636</v>
-      </c>
-      <c r="B486" t="n">
-        <v>2</v>
-      </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>Hai Hang You 7</t>
-        </is>
-      </c>
-      <c r="D486" t="inlineStr">
-        <is>
-          <t>Zhongdayou288</t>
-        </is>
-      </c>
-      <c r="E486" t="inlineStr"/>
-      <c r="F486" t="inlineStr"/>
-      <c r="G486" t="inlineStr"/>
-      <c r="H486" t="inlineStr"/>
-      <c r="I486" t="inlineStr"/>
-      <c r="J486" t="inlineStr"/>
-      <c r="K486" t="inlineStr"/>
-    </row>
-    <row r="487">
-      <c r="A487" t="n">
-        <v>1637</v>
-      </c>
-      <c r="B487" t="n">
-        <v>3</v>
-      </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>Zhongdayou288</t>
-        </is>
-      </c>
-      <c r="D487" t="inlineStr">
-        <is>
-          <t>Jin Shi 77</t>
-        </is>
-      </c>
-      <c r="E487" t="inlineStr">
-        <is>
-          <t>Fu Jie 168</t>
-        </is>
-      </c>
-      <c r="F487" t="inlineStr"/>
-      <c r="G487" t="inlineStr"/>
-      <c r="H487" t="inlineStr"/>
-      <c r="I487" t="inlineStr"/>
-      <c r="J487" t="inlineStr"/>
-      <c r="K487" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
